--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/03_Tasarım Doğrulama, Test ve Onay/EKG-TAS-PLN-01_tasarim_dogrulama_ve_gecerli_kilma_test_plani__dvpr.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/03_Tasarım Doğrulama, Test ve Onay/EKG-TAS-PLN-01_tasarim_dogrulama_ve_gecerli_kilma_test_plani__dvpr.xlsx
@@ -900,7 +900,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-PLN-01&amp;C&amp;"Arial,Regular"&amp;11Tasarım Doğrulama ve Geçerli Kılma Test Planı - DVPR</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 08.09.2026
+Revizyon nedeni: DVP&amp;&amp;R planı ve gerçekleşen sonuç ayrıldı; numune/revizyon ve kaynaklı test kabul zinciri kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1079,7 +1080,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-PLN-01&amp;C&amp;"Arial,Regular"&amp;11Tasarım Doğrulama ve Geçerli Kılma Test Planı - DVPR</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 08.09.2026
+Revizyon nedeni: DVP&amp;&amp;R planı ve gerçekleşen sonuç ayrıldı; numune/revizyon ve kaynaklı test kabul zinciri kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>